--- a/data/H131_20260625_14.xlsx
+++ b/data/H131_20260625_14.xlsx
@@ -2457,7 +2457,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>1117.0</v>
+        <v>1176.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2469,16 +2469,16 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>1117.0</v>
+        <v>1176.0</v>
       </c>
       <c r="O29" s="2">
-        <v>434.0</v>
+        <v>445.0</v>
       </c>
       <c r="P29" s="2">
-        <v>427.0</v>
+        <v>437.0</v>
       </c>
       <c r="Q29" s="2">
-        <v>256.0</v>
+        <v>294.0</v>
       </c>
       <c r="R29" s="2">
         <v>47.0</v>
@@ -5121,7 +5121,7 @@
         <v>522.0</v>
       </c>
       <c r="J65" s="2">
-        <v>503.0</v>
+        <v>508.0</v>
       </c>
       <c r="K65" s="2">
         <v>1.0</v>
@@ -5133,16 +5133,16 @@
         <v>0.0</v>
       </c>
       <c r="N65" s="2">
-        <v>500.0</v>
+        <v>508.0</v>
       </c>
       <c r="O65" s="2">
-        <v>290.0</v>
+        <v>291.0</v>
       </c>
       <c r="P65" s="2">
         <v>212.0</v>
       </c>
       <c r="Q65" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="R65" s="2">
         <v>10.0</v>
@@ -5154,13 +5154,13 @@
         <v>3.0</v>
       </c>
       <c r="U65" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="V65" s="2">
         <v>0.0</v>
       </c>
       <c r="W65" s="2">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="X65" s="1">
         <v>1.0</v>
@@ -5861,7 +5861,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" s="2">
-        <v>823.0</v>
+        <v>824.0</v>
       </c>
       <c r="K75" s="2">
         <v>1.0</v>
@@ -5873,10 +5873,10 @@
         <v>0.0</v>
       </c>
       <c r="N75" s="2">
-        <v>823.0</v>
+        <v>824.0</v>
       </c>
       <c r="O75" s="2">
-        <v>428.0</v>
+        <v>429.0</v>
       </c>
       <c r="P75" s="2">
         <v>379.0</v>
@@ -5894,13 +5894,13 @@
         <v>2.0</v>
       </c>
       <c r="U75" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="V75" s="2">
         <v>0.0</v>
       </c>
       <c r="W75" s="2">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
       <c r="X75" s="1">
         <v>1.0</v>
@@ -5935,7 +5935,7 @@
         <v>970.0</v>
       </c>
       <c r="J76" s="2">
-        <v>893.0</v>
+        <v>894.0</v>
       </c>
       <c r="K76" s="2">
         <v>1.0</v>
@@ -5947,19 +5947,19 @@
         <v>0.0</v>
       </c>
       <c r="N76" s="2">
-        <v>893.0</v>
+        <v>894.0</v>
       </c>
       <c r="O76" s="2">
         <v>487.0</v>
       </c>
       <c r="P76" s="2">
-        <v>406.0</v>
+        <v>407.0</v>
       </c>
       <c r="Q76" s="2">
         <v>0.0</v>
       </c>
       <c r="R76" s="2">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="S76" s="2">
         <v>33.0</v>
@@ -5974,7 +5974,7 @@
         <v>0.0</v>
       </c>
       <c r="W76" s="2">
-        <v>78.0</v>
+        <v>77.0</v>
       </c>
       <c r="X76" s="1">
         <v>1.0</v>
@@ -11189,7 +11189,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>1205.0</v>
+        <v>1207.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -11201,19 +11201,19 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>1205.0</v>
+        <v>1207.0</v>
       </c>
       <c r="O147" s="2">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="P147" s="2">
         <v>572.0</v>
       </c>
       <c r="Q147" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R147" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="S147" s="2">
         <v>3.0</v>
@@ -11228,7 +11228,7 @@
         <v>0.0</v>
       </c>
       <c r="W147" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="X147" s="1">
         <v>1.0</v>
@@ -12225,7 +12225,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>1323.0</v>
+        <v>1336.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -12237,10 +12237,10 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>1323.0</v>
+        <v>1336.0</v>
       </c>
       <c r="O161" s="2">
-        <v>732.0</v>
+        <v>745.0</v>
       </c>
       <c r="P161" s="2">
         <v>567.0</v>
@@ -12249,7 +12249,7 @@
         <v>24.0</v>
       </c>
       <c r="R161" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="S161" s="2">
         <v>18.0</v>
@@ -12264,7 +12264,7 @@
         <v>0.0</v>
       </c>
       <c r="W161" s="2">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="X161" s="1">
         <v>1.0</v>
@@ -12521,7 +12521,7 @@
         <v>421.0</v>
       </c>
       <c r="J165" s="2">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="K165" s="2">
         <v>1.0</v>
@@ -12533,10 +12533,10 @@
         <v>0.0</v>
       </c>
       <c r="N165" s="2">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="O165" s="2">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="P165" s="2">
         <v>150.0</v>
@@ -12548,7 +12548,7 @@
         <v>9.0</v>
       </c>
       <c r="S165" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T165" s="2">
         <v>0.0</v>
@@ -12560,7 +12560,7 @@
         <v>1.0</v>
       </c>
       <c r="W165" s="2">
-        <v>71.0</v>
+        <v>70.0</v>
       </c>
       <c r="X165" s="1">
         <v>1.0</v>
@@ -13335,7 +13335,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>896.0</v>
+        <v>897.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -13347,10 +13347,10 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>896.0</v>
+        <v>897.0</v>
       </c>
       <c r="O176" s="2">
-        <v>439.0</v>
+        <v>440.0</v>
       </c>
       <c r="P176" s="2">
         <v>452.0</v>
@@ -13368,13 +13368,13 @@
         <v>1.0</v>
       </c>
       <c r="U176" s="2">
-        <v>52.0</v>
+        <v>51.0</v>
       </c>
       <c r="V176" s="2">
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>149.0</v>
+        <v>148.0</v>
       </c>
       <c r="X176" s="1">
         <v>1.0</v>
@@ -13424,16 +13424,16 @@
         <v>939.0</v>
       </c>
       <c r="O177" s="2">
-        <v>554.0</v>
+        <v>555.0</v>
       </c>
       <c r="P177" s="2">
-        <v>385.0</v>
+        <v>384.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
       </c>
       <c r="R177" s="2">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="S177" s="2">
         <v>55.0</v>
@@ -13442,7 +13442,7 @@
         <v>5.0</v>
       </c>
       <c r="U177" s="2">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="V177" s="2">
         <v>0.0</v>
@@ -13557,7 +13557,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>976.0</v>
+        <v>977.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13569,19 +13569,19 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>976.0</v>
+        <v>977.0</v>
       </c>
       <c r="O179" s="2">
         <v>597.0</v>
       </c>
       <c r="P179" s="2">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
       <c r="S179" s="2">
         <v>14.0</v>
@@ -13596,7 +13596,7 @@
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>85.0</v>
+        <v>84.0</v>
       </c>
       <c r="X179" s="1">
         <v>1.0</v>
@@ -14519,7 +14519,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>470.0</v>
+        <v>467.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -14531,19 +14531,19 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>470.0</v>
+        <v>467.0</v>
       </c>
       <c r="O192" s="2">
         <v>294.0</v>
       </c>
       <c r="P192" s="2">
-        <v>171.0</v>
+        <v>168.0</v>
       </c>
       <c r="Q192" s="2">
         <v>5.0</v>
       </c>
       <c r="R192" s="2">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="S192" s="2">
         <v>5.0</v>
@@ -14558,7 +14558,7 @@
         <v>0.0</v>
       </c>
       <c r="W192" s="2">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
       <c r="X192" s="1">
         <v>1.0</v>
@@ -14608,13 +14608,13 @@
         <v>1284.0</v>
       </c>
       <c r="O193" s="2">
-        <v>555.0</v>
+        <v>559.0</v>
       </c>
       <c r="P193" s="2">
-        <v>571.0</v>
+        <v>572.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>158.0</v>
+        <v>153.0</v>
       </c>
       <c r="R193" s="2">
         <v>33.0</v>
@@ -14830,13 +14830,13 @@
         <v>1307.0</v>
       </c>
       <c r="O196" s="2">
-        <v>587.0</v>
+        <v>620.0</v>
       </c>
       <c r="P196" s="2">
         <v>544.0</v>
       </c>
       <c r="Q196" s="2">
-        <v>176.0</v>
+        <v>143.0</v>
       </c>
       <c r="R196" s="2">
         <v>38.0</v>
@@ -15259,7 +15259,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>1100.0</v>
+        <v>1105.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -15271,10 +15271,10 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>1100.0</v>
+        <v>1105.0</v>
       </c>
       <c r="O202" s="2">
-        <v>668.0</v>
+        <v>673.0</v>
       </c>
       <c r="P202" s="2">
         <v>432.0</v>
@@ -15286,10 +15286,10 @@
         <v>8.0</v>
       </c>
       <c r="S202" s="2">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="T202" s="2">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
       <c r="U202" s="2">
         <v>12.0</v>
@@ -15298,7 +15298,7 @@
         <v>1.0</v>
       </c>
       <c r="W202" s="2">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
       <c r="X202" s="1">
         <v>1.0</v>
@@ -15333,7 +15333,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>1099.0</v>
+        <v>1101.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -15345,22 +15345,22 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>1099.0</v>
+        <v>1101.0</v>
       </c>
       <c r="O203" s="2">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="P203" s="2">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="Q203" s="2">
         <v>4.0</v>
       </c>
       <c r="R203" s="2">
-        <v>79.0</v>
+        <v>78.0</v>
       </c>
       <c r="S203" s="2">
-        <v>64.0</v>
+        <v>63.0</v>
       </c>
       <c r="T203" s="2">
         <v>13.0</v>
@@ -15372,7 +15372,7 @@
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>158.0</v>
+        <v>156.0</v>
       </c>
       <c r="X203" s="1">
         <v>1.0</v>
@@ -15777,7 +15777,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>840.0</v>
+        <v>841.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15789,13 +15789,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>840.0</v>
+        <v>841.0</v>
       </c>
       <c r="O209" s="2">
         <v>437.0</v>
       </c>
       <c r="P209" s="2">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
@@ -15804,7 +15804,7 @@
         <v>48.0</v>
       </c>
       <c r="S209" s="2">
-        <v>56.0</v>
+        <v>55.0</v>
       </c>
       <c r="T209" s="2">
         <v>6.0</v>
@@ -15816,7 +15816,7 @@
         <v>1.0</v>
       </c>
       <c r="W209" s="2">
-        <v>111.0</v>
+        <v>110.0</v>
       </c>
       <c r="X209" s="1">
         <v>1.0</v>
@@ -15937,7 +15937,7 @@
         <v>0.0</v>
       </c>
       <c r="N211" s="2">
-        <v>918.0</v>
+        <v>917.0</v>
       </c>
       <c r="O211" s="2">
         <v>469.0</v>
@@ -16147,7 +16147,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>887.0</v>
+        <v>894.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -16159,22 +16159,22 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>887.0</v>
+        <v>894.0</v>
       </c>
       <c r="O214" s="2">
-        <v>473.0</v>
+        <v>474.0</v>
       </c>
       <c r="P214" s="2">
-        <v>414.0</v>
+        <v>420.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
       </c>
       <c r="R214" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="S214" s="2">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
       <c r="T214" s="2">
         <v>7.0</v>
@@ -16186,7 +16186,7 @@
         <v>5.0</v>
       </c>
       <c r="W214" s="2">
-        <v>145.0</v>
+        <v>144.0</v>
       </c>
       <c r="X214" s="1">
         <v>1.0</v>
@@ -16369,7 +16369,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>1010.0</v>
+        <v>1011.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -16381,10 +16381,10 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>1010.0</v>
+        <v>1011.0</v>
       </c>
       <c r="O217" s="2">
-        <v>512.0</v>
+        <v>513.0</v>
       </c>
       <c r="P217" s="2">
         <v>482.0</v>
@@ -16396,7 +16396,7 @@
         <v>41.0</v>
       </c>
       <c r="S217" s="2">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
       <c r="T217" s="2">
         <v>21.0</v>
@@ -16408,7 +16408,7 @@
         <v>0.0</v>
       </c>
       <c r="W217" s="2">
-        <v>126.0</v>
+        <v>125.0</v>
       </c>
       <c r="X217" s="1">
         <v>1.0</v>
@@ -16443,7 +16443,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>1063.0</v>
+        <v>1064.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -16455,13 +16455,13 @@
         <v>0.0</v>
       </c>
       <c r="N218" s="2">
-        <v>1063.0</v>
+        <v>1064.0</v>
       </c>
       <c r="O218" s="2">
         <v>548.0</v>
       </c>
       <c r="P218" s="2">
-        <v>515.0</v>
+        <v>516.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
@@ -16470,7 +16470,7 @@
         <v>61.0</v>
       </c>
       <c r="S218" s="2">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="T218" s="2">
         <v>13.0</v>
@@ -16482,7 +16482,7 @@
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>134.0</v>
+        <v>133.0</v>
       </c>
       <c r="X218" s="1">
         <v>1.0</v>
@@ -16680,13 +16680,13 @@
         <v>823.0</v>
       </c>
       <c r="O221" s="2">
-        <v>259.0</v>
+        <v>270.0</v>
       </c>
       <c r="P221" s="2">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="Q221" s="2">
-        <v>244.0</v>
+        <v>232.0</v>
       </c>
       <c r="R221" s="2">
         <v>9.0</v>
